--- a/data/S2000_01_FINAL.xlsx
+++ b/data/S2000_01_FINAL.xlsx
@@ -24,8 +24,11 @@
     <sheet name="SERIES" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="CLUBS" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="META" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="TODO" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$9</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -33,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,8 +51,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -71,6 +78,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -84,12 +96,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -17062,7 +17080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17106,6 +17124,117 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S2000_01_0104 'Sokol Hnidousy – Motyčín' prev→CLUB_S1999_00_0118 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S2000_01_0264 'Trutnov B' prev→CLUB_S1999_00_0244 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2000_01_0030 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2000_01_0031 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2000_01_0032 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0021</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2000_01_0021 'Baráž o Extraligu' (L15, parent=NODE_S2000_01_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0028</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2000_01_0028 'Baráž o I.ligu' (L15, parent=NODE_S2000_01_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0042</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2000_01_0042 'O postup do I.ligy' (L25, parent=NODE_S2000_01_0036) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -20782,8 +20911,6 @@
         </is>
       </c>
     </row>
-    <row r="88"/>
-    <row r="89"/>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
@@ -20863,7 +20990,6 @@
         </is>
       </c>
     </row>
-    <row r="97"/>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
@@ -41151,6 +41277,237 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0104</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0104 'Sokol Hnidousy – Motyčín' prev→CLUB_S1999_00_0118 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0264</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0264 'Trutnov B' prev→CLUB_S1999_00_0244 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0030</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0030 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0031</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0031 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0032</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0032 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0021</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2000_01_0021 'Baráž o Extraligu' (L15, parent=NODE_S2000_01_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0028</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2000_01_0028 'Baráž o I.ligu' (L15, parent=NODE_S2000_01_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0042</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2000_01_0042 'O postup do I.ligy' (L25, parent=NODE_S2000_01_0036) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S2000_01_FINAL.xlsx
+++ b/data/S2000_01_FINAL.xlsx
@@ -27,7 +27,7 @@
     <sheet name="TODO" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -17080,7 +17080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17130,7 +17130,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S2000_01_0104 'Sokol Hnidousy – Motyčín' prev→CLUB_S1999_00_0118 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -17142,7 +17142,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S2000_01_0264 'Trutnov B' prev→CLUB_S1999_00_0244 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -17154,7 +17154,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2000_01_0030 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -17166,7 +17166,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2000_01_0031 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -17178,7 +17178,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2000_01_0032 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -17188,14 +17188,9 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>NODE_S2000_01_0021</t>
-        </is>
-      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2000_01_0021 'Baráž o Extraligu' (L15, parent=NODE_S2000_01_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -17205,14 +17200,9 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>NODE_S2000_01_0028</t>
-        </is>
-      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2000_01_0028 'Baráž o I.ligu' (L15, parent=NODE_S2000_01_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -17222,17 +17212,514 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>NODE_S2000_01_0042</t>
-        </is>
-      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2000_01_0042 'O postup do I.ligy' (L25, parent=NODE_S2000_01_0036) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0052 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0118 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0188 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'PSV Litoměřice' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Louny' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0256 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0257 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0244 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Ústí nad Labem' → 'Ústí nad Orlicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Red Bears Prostějov' → 'Prostějov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Orli Znojmo B' → 'Znojmo B' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Florida Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Buly Centrum Kravaře' → 'Kravaře' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0030</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina Čechy'</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0031</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina Morava'</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -20911,6 +21398,8 @@
         </is>
       </c>
     </row>
+    <row r="88"/>
+    <row r="89"/>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
@@ -20941,6 +21430,11 @@
           <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0001</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -20953,6 +21447,11 @@
           <t>Kvalifikace o II.ligu</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0003</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -20965,6 +21464,11 @@
           <t>Krajské přebory (nové velké kraje!)</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0003</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -20977,6 +21481,11 @@
           <t>I.třída / I.B třída / Krajská soutěž</t>
         </is>
       </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0036</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -20990,6 +21499,7 @@
         </is>
       </c>
     </row>
+    <row r="97"/>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
@@ -23897,12 +24407,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -23981,12 +24491,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -24149,12 +24659,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov.</t>
+          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov. || TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>KLH VT VTJ Chomutov</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -24527,12 +25037,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Slezan Opava</t>
         </is>
       </c>
     </row>
@@ -24616,12 +25126,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -24789,12 +25299,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -24905,12 +25415,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Jablonec nad Nisou = HC Vlci Jablonec nL Nisou (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. city Jablonec nad Nisou.</t>
+          <t>Jablonec nad Nisou = HC Vlci Jablonec nL Nisou (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. city Jablonec nad Nisou. || TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Vlci Jablonec nad Nisou</t>
+          <t>Jablonec nad Nisou</t>
         </is>
       </c>
     </row>
@@ -25352,12 +25862,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -25399,12 +25909,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -25483,12 +25993,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -25693,12 +26203,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Nymburk = NED Hockey Nymburk (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. Post-revolucni. city Nymburk.</t>
+          <t>Nymburk = NED Hockey Nymburk (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. Post-revolucni. city Nymburk. || TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>NED Hockey Nymburk</t>
+          <t>Nymburk</t>
         </is>
       </c>
     </row>
@@ -25945,12 +26455,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Slaný = HK Lev Slaný (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). '(II)' = druzstvo II. city Slaný.</t>
+          <t>Slaný = HK Lev Slaný (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). '(II)' = druzstvo II. city Slaný. || TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>HK Lev Slaný</t>
+          <t>Slaný</t>
         </is>
       </c>
     </row>
@@ -26291,12 +26801,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -26412,12 +26922,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště.</t>
+          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště. || TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Slovácká Slavia Uherské Hradiště</t>
+          <t>Uherské Hradiště</t>
         </is>
       </c>
     </row>
@@ -26622,12 +27132,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -28145,12 +28655,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -28229,12 +28739,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -28486,12 +28996,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -28748,12 +29258,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -28837,12 +29347,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -28931,12 +29441,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -31846,12 +32356,12 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště.</t>
+          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště. || TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>Slovácká Slavia Uherské Hradiště</t>
+          <t>Uherské Hradiště</t>
         </is>
       </c>
     </row>
@@ -33122,12 +33632,12 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -33206,12 +33716,12 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>Litoměřice = HC PSV Litoměřice (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **PSV** = Policejni sportovni vychova. city Litoměřice.</t>
+          <t>Litoměřice = HC PSV Litoměřice (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **PSV** = Policejni sportovni vychova. city Litoměřice. || TBD: city 'PSV Litoměřice' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>PSV Litoměřice</t>
+          <t>Jablonec nad Nisou</t>
         </is>
       </c>
     </row>
@@ -33332,12 +33842,12 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>Oprava city: „Louky" → „Louky (UNL)". TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo. || Oprava clean+city: "Louky" → "Louny" (překlep almanachu, Pavlovo upresneni 04/2026 - district "skupina B" v Ústeckém kraji = okres Louny). prev=CLUB_S1951_52_0427 byl chybný (ukazoval na Karviná) - k overeni Pavlem. || Louny = Slovan Louny (Wiki D42 - registr ustavy 04/2026). Hlavni okresni klub. Genealogie: Cechie Louny (49/50) -&gt; VSJ -&gt; Slovan Louny. city Louny.</t>
+          <t>Oprava city: „Louky" → „Louky (UNL)". TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo. || Oprava clean+city: "Louky" → "Louny" (překlep almanachu, Pavlovo upresneni 04/2026 - district "skupina B" v Ústeckém kraji = okres Louny). prev=CLUB_S1951_52_0427 byl chybný (ukazoval na Karviná) - k overeni Pavlem. || Louny = Slovan Louny (Wiki D42 - registr ustavy 04/2026). Hlavni okresni klub. Genealogie: Cechie Louny (49/50) -&gt; VSJ -&gt; Slovan Louny. city Louny. || TBD: city 'Louny' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>Louny</t>
+          <t>Jablonec nad Nisou</t>
         </is>
       </c>
     </row>
@@ -34056,12 +34566,12 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Nový Bydžov</t>
         </is>
       </c>
     </row>
@@ -35010,12 +35520,12 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Ústí nad Labem' → 'Ústí nad Orlicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Orlicí</t>
         </is>
       </c>
     </row>
@@ -37946,12 +38456,12 @@
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>Prostějov = HC Red Bears Prostějov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj. city Prostějov.</t>
+          <t>Prostějov = HC Red Bears Prostějov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj. city Prostějov. || TBD: city 'Red Bears Prostějov' → 'Prostějov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>Red Bears Prostějov</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -38732,12 +39242,12 @@
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>Znojmo = SK Znojemští Orli B (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. 'B' = druzstvo B. city Znojmo.</t>
+          <t>Znojmo = SK Znojemští Orli B (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. 'B' = druzstvo B. city Znojmo. || TBD: city 'Orli Znojmo B' → 'Znojmo B' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>Orli Znojmo B</t>
+          <t>Znojmo B</t>
         </is>
       </c>
     </row>
@@ -39335,12 +39845,12 @@
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -39555,12 +40065,12 @@
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -39785,12 +40295,12 @@
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>Velké Meziříčí = HC Florida Velké Meziříčí (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. Post-revolucni nazev. city Velké Meziříčí.</t>
+          <t>Velké Meziříčí = HC Florida Velké Meziříčí (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. Post-revolucni nazev. city Velké Meziříčí. || TBD: city 'Florida Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>Florida Velké Meziříčí</t>
+          <t>Velké Meziříčí</t>
         </is>
       </c>
     </row>
@@ -40398,12 +40908,12 @@
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>Kravaře = HC Buly Centrum Kravaře (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). city Kravaře.</t>
+          <t>Kravaře = HC Buly Centrum Kravaře (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). city Kravaře. || TBD: city 'Buly Centrum Kravaře' → 'Kravaře' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>Buly Centrum Kravaře</t>
+          <t>Kravaře</t>
         </is>
       </c>
     </row>
@@ -41287,11 +41797,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -41336,21 +41846,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0104</t>
+          <t>CLUB_S2000_01_0009</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0104 'Sokol Hnidousy – Motyčín' prev→CLUB_S1999_00_0118 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -41358,21 +41866,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0264</t>
+          <t>CLUB_S2000_01_0011</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0264 'Trutnov B' prev→CLUB_S1999_00_0244 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -41380,21 +41886,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0030</t>
+          <t>CLUB_S2000_01_0015</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0030 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -41402,21 +41906,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0031</t>
+          <t>CLUB_S2000_01_0024</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0031 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -41424,21 +41926,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0032</t>
+          <t>CLUB_S2000_01_0026</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0032 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -41446,21 +41946,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NODE_S2000_01_0021</t>
+          <t>CLUB_S2000_01_0030</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2000_01_0021 'Baráž o Extraligu' (L15, parent=NODE_S2000_01_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -41468,21 +41966,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NODE_S2000_01_0028</t>
+          <t>CLUB_S2000_01_0034</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2000_01_0028 'Baráž o I.ligu' (L15, parent=NODE_S2000_01_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -41490,24 +41986,842 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NODE_S2000_01_0042</t>
+          <t>CLUB_S2000_01_0042</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2000_01_0042 'O postup do I.ligy' (L25, parent=NODE_S2000_01_0036) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0052 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0049</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0050</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0053</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0058</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0064</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0072</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0076</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0081</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0104</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0118 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0116</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0116</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0118</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0124</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0130</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0132</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0134</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0189</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0188 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0200</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0227</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0229</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0231</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'PSV Litoměřice' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0232</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0234</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0234</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Louny' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0238</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0241</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0256 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0243</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0257 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0246</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0252</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0264</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0244 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0274</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0274</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Ústí nad Labem' → 'Ústí nad Orlicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0282</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0344</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Red Bears Prostějov' → 'Prostějov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0362</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Orli Znojmo B' → 'Znojmo B' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0376</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0381</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0386</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Florida Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>CLUB_S2000_01_0401</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Buly Centrum Kravaře' → 'Kravaře' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0030</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina Čechy'</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0031</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina Morava'</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F9"/>
+  <autoFilter ref="A1:F50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -60123,6 +61437,11 @@
           <t>CLUB_S1999_00_0233</t>
         </is>
       </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>zanik</t>
+        </is>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>TR_S2000_01_00158</t>
@@ -60168,6 +61487,11 @@
       <c r="R12" t="inlineStr">
         <is>
           <t>CLUB_S1999_00_0230</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>zanik</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -60258,6 +61582,11 @@
           <t>CLUB_S1999_00_0233</t>
         </is>
       </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>sestup</t>
+        </is>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>TR_S2000_01_00160</t>
@@ -60346,6 +61675,11 @@
           <t>CLUB_S1999_00_0230</t>
         </is>
       </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>zanik</t>
+        </is>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>TR_S2000_01_00161</t>

--- a/data/S2000_01_FINAL.xlsx
+++ b/data/S2000_01_FINAL.xlsx
@@ -27,7 +27,7 @@
     <sheet name="TODO" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -17080,7 +17080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17142,7 +17142,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -17154,7 +17154,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -17166,7 +17166,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -17178,7 +17178,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0052 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -17190,7 +17190,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -17202,7 +17202,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -17214,7 +17214,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0052 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -17226,7 +17226,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -17238,7 +17238,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -17250,7 +17250,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -17262,7 +17262,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0118 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -17274,7 +17274,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -17286,7 +17286,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -17298,7 +17298,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -17310,7 +17310,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0188 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -17322,7 +17322,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0118 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -17334,7 +17334,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -17346,7 +17346,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -17358,7 +17358,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -17370,7 +17370,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -17382,7 +17382,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -17394,7 +17394,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0256 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -17406,7 +17406,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0257 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -17418,7 +17418,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0188 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -17430,7 +17430,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0244 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -17442,7 +17442,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -17454,7 +17454,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -17466,7 +17466,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'PSV Litoměřice' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Red Bears Prostějov' → 'Prostějov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -17478,7 +17478,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Orli Znojmo B' → 'Znojmo B' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -17490,7 +17490,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -17502,7 +17502,7 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Louny' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -17514,7 +17514,7 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Florida Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -17526,7 +17526,7 @@
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0256 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Buly Centrum Kravaře' → 'Kravaře' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -17536,9 +17536,14 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0030</t>
+        </is>
+      </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0257 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina Čechy'</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -17548,178 +17553,17 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0031</t>
+        </is>
+      </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina Morava'</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0244 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Ústí nad Labem' → 'Ústí nad Orlicí' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Red Bears Prostějov' → 'Prostějov' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Orli Znojmo B' → 'Znojmo B' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Florida Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Buly Centrum Kravaře' → 'Kravaře' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>NODE_S2000_01_0030</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina Čechy'</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>NODE_S2000_01_0031</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina Morava'</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -17736,7 +17580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:L101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17795,6 +17639,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17837,6 +17686,11 @@
           <t>14 týmů (5 stat sloupců): základ + QF/SF/finále + baráž. Mistr: HC Slovnaft Vsetín (6. titul).</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17884,6 +17738,11 @@
           <t>Vítězové 4 skupin II.ligy. Dvoukolově. Top 2 do I.ligy.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -17926,6 +17785,11 @@
           <t>I.ČNHL: základ + playoff (QF/SF/finále/O 3.) + O 5.-8. + o udržení. I.SNHL (12). Kval o I.ligu.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -17968,6 +17832,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -18010,6 +17879,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18052,6 +17926,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18094,6 +17973,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -18136,6 +18020,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -18178,6 +18067,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -18220,6 +18114,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -18262,6 +18161,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -18304,6 +18208,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -18346,6 +18255,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18388,6 +18302,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -18430,6 +18349,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -18472,6 +18396,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0016</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -18514,6 +18443,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0017</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -18556,6 +18490,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0018</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -18598,6 +18537,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0019</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -18640,6 +18584,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0020</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -18682,6 +18631,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0021</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -18724,6 +18678,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0022</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -18766,6 +18725,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0023</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -18808,6 +18772,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0024</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -18850,6 +18819,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -18892,6 +18866,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0026</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -18934,6 +18913,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0027</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -19023,6 +19007,11 @@
           <t>Kvalifikace o postup do II.ligy</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0029</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -19129,6 +19118,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0034</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -19255,6 +19249,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0037</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -19297,6 +19296,11 @@
           <t>II.liga: 2 skupiny + finále + o postup do I.ligy.</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0041</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -19339,6 +19343,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0042</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -19381,6 +19390,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0043</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -19423,6 +19437,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0044</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -19465,6 +19484,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0045</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -19507,6 +19531,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0046</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -19549,6 +19578,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0047</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -19591,6 +19625,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0048</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -19633,6 +19672,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0049</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -19675,6 +19719,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0050</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -19717,6 +19766,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0051</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -19801,6 +19855,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0057</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -19843,6 +19902,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0058</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -19885,6 +19949,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0059</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -19927,6 +19996,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0060</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -19969,6 +20043,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0061</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -20011,6 +20090,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0062</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -20053,6 +20137,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0063</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -20095,6 +20184,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0064</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -20137,6 +20231,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0065</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -20305,6 +20404,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0076</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -20347,6 +20451,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0077</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -20389,6 +20498,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0078</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -20473,6 +20587,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0080</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -20515,6 +20634,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0081</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -20557,6 +20681,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0082</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -20599,6 +20728,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0083</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -20809,6 +20943,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0090</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -20851,6 +20990,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0091</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -20893,6 +21037,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0092</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -20977,6 +21126,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0093</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -21061,6 +21215,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0096</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -21355,6 +21514,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0099</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -21395,6 +21559,11 @@
       <c r="K87" t="inlineStr">
         <is>
           <t>Kontejner L50</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0100</t>
         </is>
       </c>
     </row>
@@ -21418,6 +21587,11 @@
           <t>I.liga (10 týmů, jeden stůl)</t>
         </is>
       </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>L10</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -21435,6 +21609,11 @@
           <t>NODE_S2000_01_0001</t>
         </is>
       </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -21452,6 +21631,11 @@
           <t>NODE_S2000_01_0003</t>
         </is>
       </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -21469,6 +21653,11 @@
           <t>NODE_S2000_01_0003</t>
         </is>
       </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -21486,6 +21675,11 @@
           <t>NODE_S2000_01_0036</t>
         </is>
       </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -21496,6 +21690,11 @@
       <c r="B96" t="inlineStr">
         <is>
           <t>Okresní přebory (jen registr)</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>okresní</t>
         </is>
       </c>
     </row>
@@ -24491,12 +24690,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -25037,12 +25236,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Slezan Opava</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -25299,12 +25498,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -25862,12 +26061,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -27132,12 +27331,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -28655,12 +28854,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -28739,12 +28938,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -28996,12 +29195,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -29258,12 +29457,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -33716,12 +33915,12 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>Litoměřice = HC PSV Litoměřice (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **PSV** = Policejni sportovni vychova. city Litoměřice. || TBD: city 'PSV Litoměřice' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Litoměřice = HC PSV Litoměřice (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **PSV** = Policejni sportovni vychova. city Litoměřice.</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>Jablonec nad Nisou</t>
+          <t>Litoměřice</t>
         </is>
       </c>
     </row>
@@ -33842,12 +34041,12 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>Oprava city: „Louky" → „Louky (UNL)". TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo. || Oprava clean+city: "Louky" → "Louny" (překlep almanachu, Pavlovo upresneni 04/2026 - district "skupina B" v Ústeckém kraji = okres Louny). prev=CLUB_S1951_52_0427 byl chybný (ukazoval na Karviná) - k overeni Pavlem. || Louny = Slovan Louny (Wiki D42 - registr ustavy 04/2026). Hlavni okresni klub. Genealogie: Cechie Louny (49/50) -&gt; VSJ -&gt; Slovan Louny. city Louny. || TBD: city 'Louny' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Oprava city: „Louky" → „Louky (UNL)". TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo. || Oprava clean+city: "Louky" → "Louny" (překlep almanachu, Pavlovo upresneni 04/2026 - district "skupina B" v Ústeckém kraji = okres Louny). prev=CLUB_S1951_52_0427 byl chybný (ukazoval na Karviná) - k overeni Pavlem. || Louny = Slovan Louny (Wiki D42 - registr ustavy 04/2026). Hlavni okresni klub. Genealogie: Cechie Louny (49/50) -&gt; VSJ -&gt; Slovan Louny. city Louny.</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>Jablonec nad Nisou</t>
+          <t>Louny</t>
         </is>
       </c>
     </row>
@@ -34566,12 +34765,12 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>Nový Bydžov</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -35520,12 +35719,12 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Ústí nad Labem' → 'Ústí nad Orlicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>Ústí nad Orlicí</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -41797,7 +41996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -41871,12 +42070,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0011</t>
+          <t>CLUB_S2000_01_0015</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -41891,12 +42090,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0015</t>
+          <t>CLUB_S2000_01_0026</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -41911,12 +42110,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0024</t>
+          <t>CLUB_S2000_01_0034</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -41931,12 +42130,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0026</t>
+          <t>CLUB_S2000_01_0042</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0052 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -41951,12 +42150,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0030</t>
+          <t>CLUB_S2000_01_0050</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -41971,12 +42170,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0034</t>
+          <t>CLUB_S2000_01_0053</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -41991,12 +42190,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0042</t>
+          <t>CLUB_S2000_01_0058</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0052 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -42011,12 +42210,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0049</t>
+          <t>CLUB_S2000_01_0064</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -42031,12 +42230,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0050</t>
+          <t>CLUB_S2000_01_0072</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -42051,12 +42250,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0053</t>
+          <t>CLUB_S2000_01_0076</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -42071,12 +42270,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0058</t>
+          <t>CLUB_S2000_01_0104</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0118 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -42091,12 +42290,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0064</t>
+          <t>CLUB_S2000_01_0116</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -42111,12 +42310,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0072</t>
+          <t>CLUB_S2000_01_0132</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -42131,12 +42330,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0076</t>
+          <t>CLUB_S2000_01_0134</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -42151,12 +42350,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0081</t>
+          <t>CLUB_S2000_01_0189</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0188 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -42171,12 +42370,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0104</t>
+          <t>CLUB_S2000_01_0200</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0118 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -42191,12 +42390,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0116</t>
+          <t>CLUB_S2000_01_0227</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -42211,12 +42410,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0116</t>
+          <t>CLUB_S2000_01_0229</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -42231,12 +42430,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0118</t>
+          <t>CLUB_S2000_01_0232</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -42251,12 +42450,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0124</t>
+          <t>CLUB_S2000_01_0234</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -42271,12 +42470,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0130</t>
+          <t>CLUB_S2000_01_0238</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -42291,12 +42490,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0132</t>
+          <t>CLUB_S2000_01_0241</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0256 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -42311,12 +42510,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0134</t>
+          <t>CLUB_S2000_01_0243</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0257 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -42331,12 +42530,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0189</t>
+          <t>CLUB_S2000_01_0246</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0188 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -42351,12 +42550,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0200</t>
+          <t>CLUB_S2000_01_0264</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0244 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -42371,12 +42570,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0227</t>
+          <t>CLUB_S2000_01_0274</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -42391,12 +42590,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0229</t>
+          <t>CLUB_S2000_01_0282</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
     </row>
@@ -42411,12 +42610,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0231</t>
+          <t>CLUB_S2000_01_0344</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'PSV Litoměřice' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Red Bears Prostějov' → 'Prostějov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -42431,12 +42630,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0232</t>
+          <t>CLUB_S2000_01_0362</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: city 'Orli Znojmo B' → 'Znojmo B' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -42451,12 +42650,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0234</t>
+          <t>CLUB_S2000_01_0376</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -42471,12 +42670,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0234</t>
+          <t>CLUB_S2000_01_0381</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Louny' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -42491,12 +42690,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0238</t>
+          <t>CLUB_S2000_01_0386</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>TBD: city 'Florida Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -42511,12 +42710,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0241</t>
+          <t>CLUB_S2000_01_0401</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0256 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Buly Centrum Kravaře' → 'Kravaře' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -42526,17 +42725,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>prev_club_id / identita</t>
+          <t>pyramida (feeds_into)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0243</t>
+          <t>NODE_S2000_01_0030</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0257 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina Čechy'</t>
         </is>
       </c>
     </row>
@@ -42546,282 +42745,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>prev_club_id / identita</t>
+          <t>pyramida (feeds_into)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CLUB_S2000_01_0246</t>
+          <t>NODE_S2000_01_0031</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>CLUB_S2000_01_0252</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>CLUB_S2000_01_0264</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0244 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>CLUB_S2000_01_0274</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>CLUB_S2000_01_0274</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Ústí nad Labem' → 'Ústí nad Orlicí' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>CLUB_S2000_01_0282</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>CLUB_S2000_01_0344</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Red Bears Prostějov' → 'Prostějov' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>CLUB_S2000_01_0362</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Orli Znojmo B' → 'Znojmo B' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>CLUB_S2000_01_0376</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>CLUB_S2000_01_0381</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>CLUB_S2000_01_0386</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Florida Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>CLUB_S2000_01_0401</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Buly Centrum Kravaře' → 'Kravaře' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>pyramida (feeds_into)</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>NODE_S2000_01_0030</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina Čechy'</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>pyramida (feeds_into)</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>NODE_S2000_01_0031</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina Morava'</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F50"/>
+  <autoFilter ref="A1:F37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S2000_01_FINAL.xlsx
+++ b/data/S2000_01_FINAL.xlsx
@@ -17080,7 +17080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17128,21 +17128,26 @@
       </c>
     </row>
     <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[club-fate] TJ Hvězda Kladno — odstoupila před začátkem</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TODO-auto</t>
+          <t>club-note-extracted</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -17154,7 +17159,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -17166,7 +17171,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -17178,7 +17183,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0052 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -17190,7 +17195,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0052 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -17202,7 +17207,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -17214,7 +17219,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -17226,7 +17231,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -17238,7 +17243,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -17250,7 +17255,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -17262,7 +17267,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0118 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -17274,7 +17279,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0118 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -17286,7 +17291,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -17310,7 +17315,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0188 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -17322,7 +17327,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0188 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -17334,7 +17339,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -17346,7 +17351,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -17358,7 +17363,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -17382,7 +17387,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -17394,7 +17399,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0256 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -17406,7 +17411,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0257 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0256 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -17418,7 +17423,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0257 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -17430,7 +17435,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0244 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -17442,7 +17447,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0244 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -17454,7 +17459,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -17466,7 +17471,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Red Bears Prostějov' → 'Prostějov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -17478,7 +17483,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Orli Znojmo B' → 'Znojmo B' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Red Bears Prostějov' → 'Prostějov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -17490,7 +17495,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Orli Znojmo B' → 'Znojmo B' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -17514,7 +17519,7 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Florida Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -17526,24 +17531,19 @@
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Florida Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
           <t>[TBD] prev_club_id / identita: TBD: city 'Buly Centrum Kravaře' → 'Kravaře' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>NODE_S2000_01_0030</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina Čechy'</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -17555,15 +17555,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>NODE_S2000_01_0030</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina Čechy'</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>NODE_S2000_01_0031</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina Morava'</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -51257,7 +51274,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Krajská liga / TJ Hvězda Kladno — odstoupila před začátkem</t>
+          <t>Krajská liga</t>
         </is>
       </c>
       <c r="C14" s="2" t="n"/>

--- a/data/S2000_01_FINAL.xlsx
+++ b/data/S2000_01_FINAL.xlsx
@@ -27,7 +27,7 @@
     <sheet name="TODO" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -17080,7 +17080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17581,6 +17581,174 @@
         </is>
       </c>
       <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -42013,7 +42181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -42776,8 +42944,288 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>HC Slovnaft Vsetín</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>HC Excalibur Znojemští Orli</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>HC IPB Pojišťovna Pardubice</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>HC Chemopetrol Litvínov</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>HC Sparta Praha (C)</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>HC Vítkovice</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>HC Slavia Praha</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>HC Continental Zlín</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>HC Oceláři Třinec</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>HC Keramika Plzeň</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>HC České Budějovice</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>HC Vagnerplast Kladno</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>HC Femax Havířov</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>HC Becherovka Karlovy Vary</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F37"/>
+  <autoFilter ref="A1:F51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S2000_01_FINAL.xlsx
+++ b/data/S2000_01_FINAL.xlsx
@@ -27,7 +27,7 @@
     <sheet name="TODO" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -757,13 +757,13 @@
         <v>52</v>
       </c>
       <c r="G5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H5" t="n">
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J5" t="n">
         <v>149</v>
@@ -773,6 +773,12 @@
           <t>:</t>
         </is>
       </c>
+      <c r="L5" t="n">
+        <v>115</v>
+      </c>
+      <c r="M5" t="n">
+        <v>99</v>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>Extraliga / základní část</t>
@@ -829,13 +835,13 @@
         <v>52</v>
       </c>
       <c r="G6" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J6" t="n">
         <v>151</v>
@@ -845,6 +851,12 @@
           <t>:</t>
         </is>
       </c>
+      <c r="L6" t="n">
+        <v>139</v>
+      </c>
+      <c r="M6" t="n">
+        <v>82</v>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>Extraliga / základní část</t>
@@ -901,13 +913,13 @@
         <v>52</v>
       </c>
       <c r="G7" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H7" t="n">
         <v>8</v>
       </c>
       <c r="I7" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J7" t="n">
         <v>156</v>
@@ -917,6 +929,12 @@
           <t>:</t>
         </is>
       </c>
+      <c r="L7" t="n">
+        <v>135</v>
+      </c>
+      <c r="M7" t="n">
+        <v>82</v>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>Extraliga / základní část</t>
@@ -973,13 +991,13 @@
         <v>52</v>
       </c>
       <c r="G8" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H8" t="n">
         <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J8" t="n">
         <v>141</v>
@@ -989,6 +1007,12 @@
           <t>:</t>
         </is>
       </c>
+      <c r="L8" t="n">
+        <v>130</v>
+      </c>
+      <c r="M8" t="n">
+        <v>81</v>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>Extraliga / základní část</t>
@@ -1045,13 +1069,13 @@
         <v>52</v>
       </c>
       <c r="G9" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H9" t="n">
         <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J9" t="n">
         <v>146</v>
@@ -1061,6 +1085,12 @@
           <t>:</t>
         </is>
       </c>
+      <c r="L9" t="n">
+        <v>139</v>
+      </c>
+      <c r="M9" t="n">
+        <v>80</v>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>Extraliga / základní část</t>
@@ -1117,13 +1147,13 @@
         <v>52</v>
       </c>
       <c r="G10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H10" t="n">
         <v>10</v>
       </c>
       <c r="I10" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J10" t="n">
         <v>132</v>
@@ -1133,6 +1163,12 @@
           <t>:</t>
         </is>
       </c>
+      <c r="L10" t="n">
+        <v>126</v>
+      </c>
+      <c r="M10" t="n">
+        <v>80</v>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>Extraliga / základní část</t>
@@ -1189,13 +1225,13 @@
         <v>52</v>
       </c>
       <c r="G11" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H11" t="n">
         <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J11" t="n">
         <v>151</v>
@@ -1205,6 +1241,12 @@
           <t>:</t>
         </is>
       </c>
+      <c r="L11" t="n">
+        <v>134</v>
+      </c>
+      <c r="M11" t="n">
+        <v>79</v>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>Extraliga / základní část</t>
@@ -1261,13 +1303,13 @@
         <v>52</v>
       </c>
       <c r="G12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H12" t="n">
         <v>7</v>
       </c>
       <c r="I12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J12" t="n">
         <v>143</v>
@@ -1277,6 +1319,12 @@
           <t>:</t>
         </is>
       </c>
+      <c r="L12" t="n">
+        <v>131</v>
+      </c>
+      <c r="M12" t="n">
+        <v>79</v>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>Extraliga / základní část</t>
@@ -1333,13 +1381,13 @@
         <v>52</v>
       </c>
       <c r="G13" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H13" t="n">
         <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J13" t="n">
         <v>164</v>
@@ -1349,6 +1397,12 @@
           <t>:</t>
         </is>
       </c>
+      <c r="L13" t="n">
+        <v>163</v>
+      </c>
+      <c r="M13" t="n">
+        <v>75</v>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>Extraliga / základní část</t>
@@ -1405,13 +1459,13 @@
         <v>52</v>
       </c>
       <c r="G14" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H14" t="n">
         <v>6</v>
       </c>
       <c r="I14" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J14" t="n">
         <v>150</v>
@@ -1421,6 +1475,12 @@
           <t>:</t>
         </is>
       </c>
+      <c r="L14" t="n">
+        <v>144</v>
+      </c>
+      <c r="M14" t="n">
+        <v>74</v>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
           <t>Extraliga / základní část</t>
@@ -1477,13 +1537,13 @@
         <v>52</v>
       </c>
       <c r="G15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H15" t="n">
         <v>5</v>
       </c>
       <c r="I15" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J15" t="n">
         <v>156</v>
@@ -1493,6 +1553,12 @@
           <t>:</t>
         </is>
       </c>
+      <c r="L15" t="n">
+        <v>154</v>
+      </c>
+      <c r="M15" t="n">
+        <v>72</v>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
           <t>Extraliga / základní část</t>
@@ -1549,13 +1615,13 @@
         <v>52</v>
       </c>
       <c r="G16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H16" t="n">
         <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J16" t="n">
         <v>127</v>
@@ -1565,6 +1631,12 @@
           <t>:</t>
         </is>
       </c>
+      <c r="L16" t="n">
+        <v>176</v>
+      </c>
+      <c r="M16" t="n">
+        <v>62</v>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>Extraliga / základní část</t>
@@ -1621,13 +1693,13 @@
         <v>52</v>
       </c>
       <c r="G17" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H17" t="n">
         <v>3</v>
       </c>
       <c r="I17" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J17" t="n">
         <v>141</v>
@@ -1637,6 +1709,12 @@
           <t>:</t>
         </is>
       </c>
+      <c r="L17" t="n">
+        <v>180</v>
+      </c>
+      <c r="M17" t="n">
+        <v>62</v>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>Extraliga / základní část</t>
@@ -1693,13 +1771,13 @@
         <v>52</v>
       </c>
       <c r="G18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H18" t="n">
         <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J18" t="n">
         <v>117</v>
@@ -1708,6 +1786,12 @@
         <is>
           <t>:</t>
         </is>
+      </c>
+      <c r="L18" t="n">
+        <v>158</v>
+      </c>
+      <c r="M18" t="n">
+        <v>49</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -17080,7 +17164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17581,174 +17665,6 @@
         </is>
       </c>
       <c r="D39" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -42181,7 +42097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -42944,288 +42860,8 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>HC Slovnaft Vsetín</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>HC Excalibur Znojemští Orli</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>HC IPB Pojišťovna Pardubice</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>HC Chemopetrol Litvínov</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>HC Sparta Praha (C)</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>HC Vítkovice</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>HC Slavia Praha</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>HC Continental Zlín</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>HC Oceláři Třinec</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>HC Keramika Plzeň</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>HC České Budějovice</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>HC Vagnerplast Kladno</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>HC Femax Havířov</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>HC Becherovka Karlovy Vary</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F51"/>
+  <autoFilter ref="A1:F37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S2000_01_FINAL.xlsx
+++ b/data/S2000_01_FINAL.xlsx
@@ -17681,7 +17681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:N101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17745,6 +17745,16 @@
           <t>prev_node_id</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -21668,8 +21678,6 @@
         </is>
       </c>
     </row>
-    <row r="88"/>
-    <row r="89"/>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
@@ -21799,7 +21807,6 @@
         </is>
       </c>
     </row>
-    <row r="97"/>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>

--- a/data/S2000_01_FINAL.xlsx
+++ b/data/S2000_01_FINAL.xlsx
@@ -17933,6 +17933,16 @@
           <t>NODE_S2000_01_0001</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0010</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0016</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17947,6 +17957,14 @@
         <is>
           <t>NODE_S1999_00_0004</t>
         </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -18121,6 +18139,16 @@
           <t>NODE_S2000_01_0007</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0010</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0019</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18135,6 +18163,14 @@
         <is>
           <t>NODE_S1999_00_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -18215,6 +18251,16 @@
           <t>NODE_S2000_01_0007</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0011</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0019</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18229,6 +18275,14 @@
         <is>
           <t>NODE_S1999_00_0010</t>
         </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -18262,6 +18316,16 @@
           <t>NODE_S2000_01_0007</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0015</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0014</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18276,6 +18340,14 @@
         <is>
           <t>NODE_S1999_00_0011</t>
         </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -18309,6 +18381,8 @@
           <t>NODE_S2000_01_0007</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18323,6 +18397,14 @@
         <is>
           <t>NODE_S1999_00_0012</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -18356,6 +18438,8 @@
           <t>NODE_S2000_01_0007</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18370,6 +18454,14 @@
         <is>
           <t>NODE_S1999_00_0013</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -18403,6 +18495,8 @@
           <t>NODE_S2000_01_0007</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18417,6 +18511,14 @@
         <is>
           <t>NODE_S1999_00_0014</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -18450,6 +18552,8 @@
           <t>NODE_S2000_01_0007</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18464,6 +18568,14 @@
         <is>
           <t>NODE_S1999_00_0015</t>
         </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -18497,6 +18609,8 @@
           <t>NODE_S2000_01_0001</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18511,6 +18625,14 @@
         <is>
           <t>NODE_S1999_00_0016</t>
         </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -18544,6 +18666,8 @@
           <t>NODE_S2000_01_0007</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18558,6 +18682,14 @@
         <is>
           <t>NODE_S1999_00_0017</t>
         </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -18591,6 +18723,8 @@
           <t>NODE_S2000_01_0007</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18605,6 +18739,14 @@
         <is>
           <t>NODE_S1999_00_0018</t>
         </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>o 9. místo</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -18638,6 +18780,16 @@
           <t>NODE_S2000_01_0007</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0013</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0012</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18652,6 +18804,14 @@
         <is>
           <t>NODE_S1999_00_0019</t>
         </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -18779,6 +18939,16 @@
           <t>NODE_S2000_01_0003</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0023</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0027</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18793,6 +18963,14 @@
         <is>
           <t>NODE_S1999_00_0022</t>
         </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -18826,6 +19004,16 @@
           <t>NODE_S2000_01_0003</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0024</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0027</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18840,6 +19028,14 @@
         <is>
           <t>NODE_S1999_00_0023</t>
         </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -18873,6 +19069,12 @@
           <t>NODE_S2000_01_0003</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0025</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18887,6 +19089,14 @@
         <is>
           <t>NODE_S1999_00_0024</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -18920,6 +19130,12 @@
           <t>NODE_S2000_01_0003</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0026</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18934,6 +19150,14 @@
         <is>
           <t>NODE_S1999_00_0025</t>
         </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -18967,6 +19191,8 @@
           <t>NODE_S2000_01_0003</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18981,6 +19207,14 @@
         <is>
           <t>NODE_S1999_00_0026</t>
         </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -19014,6 +19248,8 @@
           <t>NODE_S2000_01_0003</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19028,6 +19264,14 @@
         <is>
           <t>NODE_S1999_00_0027</t>
         </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>9.–14. ZČ</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -19538,6 +19782,12 @@
           <t>NODE_S2000_01_0036</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0040</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19552,6 +19802,14 @@
         <is>
           <t>NODE_S1999_00_0044</t>
         </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -19585,6 +19843,12 @@
           <t>NODE_S2000_01_0036</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0041</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19599,6 +19863,14 @@
         <is>
           <t>NODE_S1999_00_0045</t>
         </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -19632,6 +19904,8 @@
           <t>NODE_S2000_01_0036</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19646,6 +19920,14 @@
         <is>
           <t>NODE_S1999_00_0046</t>
         </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -19773,6 +20055,8 @@
           <t>NODE_S2000_01_0036</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19787,6 +20071,14 @@
         <is>
           <t>NODE_S1999_00_0049</t>
         </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -20050,6 +20342,12 @@
           <t>NODE_S2000_01_0048</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0051</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20064,6 +20362,14 @@
         <is>
           <t>NODE_S1999_00_0059</t>
         </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -20097,6 +20403,12 @@
           <t>NODE_S2000_01_0048</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0052</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20111,6 +20423,14 @@
         <is>
           <t>NODE_S1999_00_0060</t>
         </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -20144,6 +20464,12 @@
           <t>NODE_S2000_01_0048</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0053</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20158,6 +20484,14 @@
         <is>
           <t>NODE_S1999_00_0061</t>
         </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="54">
@@ -20191,6 +20525,8 @@
           <t>NODE_S2000_01_0048</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20205,6 +20541,14 @@
         <is>
           <t>NODE_S1999_00_0062</t>
         </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="55">
@@ -20599,6 +20943,12 @@
           <t>NODE_S2000_01_0060</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0063</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20613,6 +20963,14 @@
         <is>
           <t>NODE_S1999_00_0078</t>
         </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>6 týmů</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -20646,6 +21004,12 @@
           <t>NODE_S2000_01_0060</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0065</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20655,6 +21019,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -20688,6 +21060,8 @@
           <t>NODE_S2000_01_0060</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20702,6 +21076,14 @@
         <is>
           <t>NODE_S1999_00_0080</t>
         </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="66">
@@ -20735,6 +21117,8 @@
           <t>NODE_S2000_01_0060</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20749,6 +21133,14 @@
         <is>
           <t>NODE_S1999_00_0081</t>
         </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="67">
@@ -20876,6 +21268,12 @@
           <t>NODE_S2000_01_0067</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0071</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20885,6 +21283,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -20918,6 +21324,12 @@
           <t>NODE_S2000_01_0067</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0071</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20927,6 +21339,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -21002,6 +21422,8 @@
           <t>NODE_S2000_01_0067</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21011,6 +21433,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>1.–8. ZČ</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -21138,6 +21568,16 @@
           <t>NODE_S2000_01_0072</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0075</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0080</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21152,6 +21592,14 @@
         <is>
           <t>NODE_S1999_00_0092</t>
         </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -21185,6 +21633,12 @@
           <t>NODE_S2000_01_0072</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0076</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21194,6 +21648,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="77">
@@ -21227,6 +21689,8 @@
           <t>NODE_S2000_01_0072</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21241,6 +21705,14 @@
         <is>
           <t>NODE_S1999_00_0093</t>
         </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="78">
@@ -21363,6 +21835,8 @@
           <t>NODE_S2000_01_0072</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21372,6 +21846,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="81">
@@ -21405,6 +21887,8 @@
           <t>NODE_S2000_01_0072</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21414,6 +21898,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>1.–8. ZČ</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -21489,6 +21981,8 @@
           <t>NODE_S2000_01_0072</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21498,6 +21992,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="84">
@@ -21531,6 +22033,8 @@
           <t>NODE_S2000_01_0072</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21540,6 +22044,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>1.–8. ZČ</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -21573,6 +22085,8 @@
           <t>NODE_S2000_01_0072</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21582,6 +22096,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="86">
@@ -21678,6 +22200,8 @@
         </is>
       </c>
     </row>
+    <row r="88"/>
+    <row r="89"/>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
@@ -21807,6 +22331,7 @@
         </is>
       </c>
     </row>
+    <row r="97"/>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>

--- a/data/S2000_01_FINAL.xlsx
+++ b/data/S2000_01_FINAL.xlsx
@@ -753,6 +753,11 @@
           <t>HC Slovnaft Vsetín</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F5" t="n">
         <v>52</v>
       </c>
@@ -18381,8 +18386,6 @@
           <t>NODE_S2000_01_0007</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18438,8 +18441,6 @@
           <t>NODE_S2000_01_0007</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18495,8 +18496,6 @@
           <t>NODE_S2000_01_0007</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18552,8 +18551,6 @@
           <t>NODE_S2000_01_0007</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18609,8 +18606,6 @@
           <t>NODE_S2000_01_0001</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18666,8 +18661,6 @@
           <t>NODE_S2000_01_0007</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18723,8 +18716,6 @@
           <t>NODE_S2000_01_0007</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19074,7 +19065,6 @@
           <t>NODE_S2000_01_0025</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19135,7 +19125,6 @@
           <t>NODE_S2000_01_0026</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19191,8 +19180,6 @@
           <t>NODE_S2000_01_0003</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19248,8 +19235,6 @@
           <t>NODE_S2000_01_0003</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19787,7 +19772,6 @@
           <t>NODE_S2000_01_0040</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19848,7 +19832,6 @@
           <t>NODE_S2000_01_0041</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19904,8 +19887,6 @@
           <t>NODE_S2000_01_0036</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20055,8 +20036,6 @@
           <t>NODE_S2000_01_0036</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20347,7 +20326,6 @@
           <t>NODE_S2000_01_0051</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20408,7 +20386,6 @@
           <t>NODE_S2000_01_0052</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20469,7 +20446,6 @@
           <t>NODE_S2000_01_0053</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20525,8 +20501,6 @@
           <t>NODE_S2000_01_0048</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20948,7 +20922,6 @@
           <t>NODE_S2000_01_0063</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21009,7 +20982,6 @@
           <t>NODE_S2000_01_0065</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21060,8 +21032,6 @@
           <t>NODE_S2000_01_0060</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21117,8 +21087,6 @@
           <t>NODE_S2000_01_0060</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21268,7 +21236,6 @@
           <t>NODE_S2000_01_0067</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>NODE_S2000_01_0071</t>
@@ -21324,7 +21291,6 @@
           <t>NODE_S2000_01_0067</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>NODE_S2000_01_0071</t>
@@ -21422,8 +21388,6 @@
           <t>NODE_S2000_01_0067</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21638,7 +21602,6 @@
           <t>NODE_S2000_01_0076</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21689,8 +21652,6 @@
           <t>NODE_S2000_01_0072</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21835,8 +21796,6 @@
           <t>NODE_S2000_01_0072</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21887,8 +21846,6 @@
           <t>NODE_S2000_01_0072</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21981,8 +21938,6 @@
           <t>NODE_S2000_01_0072</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22033,8 +21988,6 @@
           <t>NODE_S2000_01_0072</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22085,8 +22038,6 @@
           <t>NODE_S2000_01_0072</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22200,8 +22151,6 @@
         </is>
       </c>
     </row>
-    <row r="88"/>
-    <row r="89"/>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
@@ -22331,7 +22280,6 @@
         </is>
       </c>
     </row>
-    <row r="97"/>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
@@ -42435,7 +42383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42615,6 +42563,18 @@
       <c r="B15" t="inlineStr">
         <is>
           <t>1 oprav kvalifikačních levelů. Sloupec Q (level) aktualizován.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HC Slovnaft Vsetín</t>
         </is>
       </c>
     </row>

--- a/data/S2000_01_FINAL.xlsx
+++ b/data/S2000_01_FINAL.xlsx
@@ -22151,6 +22151,8 @@
         </is>
       </c>
     </row>
+    <row r="88"/>
+    <row r="89"/>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
@@ -22280,6 +22282,7 @@
         </is>
       </c>
     </row>
+    <row r="97"/>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>

--- a/data/S2000_01_FINAL.xlsx
+++ b/data/S2000_01_FINAL.xlsx
@@ -36,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,8 +55,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -83,6 +87,11 @@
         <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -96,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -108,6 +117,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -27527,8 +27538,6 @@
         </is>
       </c>
     </row>
-    <row r="88"/>
-    <row r="89"/>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
@@ -27658,7 +27667,6 @@
         </is>
       </c>
     </row>
-    <row r="97"/>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
@@ -54433,7 +54441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -54490,7 +54498,7 @@
           <t>CLUB_S2000_01_0009</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -54510,7 +54518,7 @@
           <t>CLUB_S2000_01_0015</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -54530,7 +54538,7 @@
           <t>CLUB_S2000_01_0026</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -54550,7 +54558,7 @@
           <t>CLUB_S2000_01_0034</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -54570,7 +54578,7 @@
           <t>CLUB_S2000_01_0042</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0052 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -54590,7 +54598,7 @@
           <t>CLUB_S2000_01_0050</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -54610,7 +54618,7 @@
           <t>CLUB_S2000_01_0053</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -54630,7 +54638,7 @@
           <t>CLUB_S2000_01_0058</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -54650,7 +54658,7 @@
           <t>CLUB_S2000_01_0064</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -54670,7 +54678,7 @@
           <t>CLUB_S2000_01_0072</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -54690,7 +54698,7 @@
           <t>CLUB_S2000_01_0076</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -54710,7 +54718,7 @@
           <t>CLUB_S2000_01_0104</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0118 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -54730,7 +54738,7 @@
           <t>CLUB_S2000_01_0116</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -54750,7 +54758,7 @@
           <t>CLUB_S2000_01_0132</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -54770,7 +54778,7 @@
           <t>CLUB_S2000_01_0134</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -54790,7 +54798,7 @@
           <t>CLUB_S2000_01_0189</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0188 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -54810,7 +54818,7 @@
           <t>CLUB_S2000_01_0200</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -54830,7 +54838,7 @@
           <t>CLUB_S2000_01_0227</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
@@ -54850,7 +54858,7 @@
           <t>CLUB_S2000_01_0229</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -54870,7 +54878,7 @@
           <t>CLUB_S2000_01_0232</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
@@ -54890,7 +54898,7 @@
           <t>CLUB_S2000_01_0234</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
@@ -54910,7 +54918,7 @@
           <t>CLUB_S2000_01_0238</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
@@ -54930,7 +54938,7 @@
           <t>CLUB_S2000_01_0241</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0256 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -54950,7 +54958,7 @@
           <t>CLUB_S2000_01_0243</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0257 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -54970,7 +54978,7 @@
           <t>CLUB_S2000_01_0246</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
@@ -54990,7 +54998,7 @@
           <t>CLUB_S2000_01_0264</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1999_00_0244 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -55010,7 +55018,7 @@
           <t>CLUB_S2000_01_0274</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -55030,7 +55038,7 @@
           <t>CLUB_S2000_01_0282</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
@@ -55050,7 +55058,7 @@
           <t>CLUB_S2000_01_0344</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>TBD: city 'Red Bears Prostějov' → 'Prostějov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -55070,7 +55078,7 @@
           <t>CLUB_S2000_01_0362</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>TBD: city 'Orli Znojmo B' → 'Znojmo B' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -55090,7 +55098,7 @@
           <t>CLUB_S2000_01_0376</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -55110,7 +55118,7 @@
           <t>CLUB_S2000_01_0381</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -55130,7 +55138,7 @@
           <t>CLUB_S2000_01_0386</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>TBD: city 'Florida Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -55150,7 +55158,7 @@
           <t>CLUB_S2000_01_0401</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>TBD: city 'Buly Centrum Kravaře' → 'Kravaře' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -55170,7 +55178,7 @@
           <t>NODE_S2000_01_0030</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina Čechy'</t>
         </is>
@@ -55190,11 +55198,141 @@
           <t>NODE_S2000_01_0031</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina Morava'</t>
         </is>
       </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>30_Severočeský L40 čtvrtfinále · NODE_S2000_01_0063</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>máme jen účastníky (Jablonec nad Nisou – PSV Litoměřice, Bílina – Slovan Louny), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>30_Severočeský L40 O 3.místo · NODE_S2000_01_0064</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>máme jen 1 tým (PSV Litoměřice – Bílina), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>30_Severočeský L40 finále · NODE_S2000_01_0065</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>máme jen účastníky (Slovan Louny – Jablonec nad Nisou), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Praha – Pražský přebor (Praha) · NODE_S2000_01_0087</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>máme jen 1 tým (HC SPEI), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Středočeský – Krajská liga (Středočeský kraj) · NODE_S2000_01_0088</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>máme jen 1 tým (TJ Hvězda Kladno), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F37"/>

--- a/data/S2000_01_FINAL.xlsx
+++ b/data/S2000_01_FINAL.xlsx
@@ -105,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -119,6 +119,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -22556,7 +22559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23057,6 +23060,91 @@
         </is>
       </c>
       <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0063</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen účastníky (Jablonec nad Nisou – PSV Litoměřice, Bílina – Slovan Louny), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0064</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 1 tým (PSV Litoměřice – Bílina), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0065</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen účastníky (Slovan Louny – Jablonec nad Nisou), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0087</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 1 tým (HC SPEI), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>NODE_S2000_01_0088</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 1 tým (TJ Hvězda Kladno), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -55218,7 +55306,7 @@
           <t>30_Severočeský L40 čtvrtfinále · NODE_S2000_01_0063</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D38" s="9" t="inlineStr">
         <is>
           <t>máme jen účastníky (Jablonec nad Nisou – PSV Litoměřice, Bílina – Slovan Louny), chybí výsledek / odveta  [torzo-audit]</t>
         </is>
@@ -55244,7 +55332,7 @@
           <t>30_Severočeský L40 O 3.místo · NODE_S2000_01_0064</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="D39" s="9" t="inlineStr">
         <is>
           <t>máme jen 1 tým (PSV Litoměřice – Bílina), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
         </is>
@@ -55270,7 +55358,7 @@
           <t>30_Severočeský L40 finále · NODE_S2000_01_0065</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D40" s="9" t="inlineStr">
         <is>
           <t>máme jen účastníky (Slovan Louny – Jablonec nad Nisou), chybí výsledek / odveta  [torzo-audit]</t>
         </is>
@@ -55296,7 +55384,7 @@
           <t>Praha – Pražský přebor (Praha) · NODE_S2000_01_0087</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="D41" s="9" t="inlineStr">
         <is>
           <t>máme jen 1 tým (HC SPEI), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
         </is>
@@ -55322,7 +55410,7 @@
           <t>Středočeský – Krajská liga (Středočeský kraj) · NODE_S2000_01_0088</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D42" s="9" t="inlineStr">
         <is>
           <t>máme jen 1 tým (TJ Hvězda Kladno), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
         </is>

--- a/data/S2000_01_FINAL.xlsx
+++ b/data/S2000_01_FINAL.xlsx
@@ -24836,7 +24836,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>KVAL  skupina Čechy</t>
+          <t>KVAL skupina Čechy</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -24868,7 +24868,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>KVAL  skupina Morava</t>
+          <t>KVAL skupina Morava</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -24900,7 +24900,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>30_Praha L40</t>
+          <t>Praha, 4. úroveň</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -24947,7 +24947,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -24989,7 +24989,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -25031,7 +25031,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>30_Praha L40 Pražský přebor</t>
+          <t>Praha, 4. úroveň Pražský přebor</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -25543,7 +25543,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>30_Středočeský L40</t>
+          <t>Středočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -25590,7 +25590,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>30_Středočeský L50</t>
+          <t>Středočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -25637,7 +25637,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 Krajská liga</t>
+          <t>Středočeský, 4. úroveň Krajská liga</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -25679,7 +25679,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40</t>
+          <t>Jihočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -25726,7 +25726,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>30_Jihočeský L50</t>
+          <t>Jihočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -25773,7 +25773,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 základní část</t>
+          <t>Jihočeský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -25833,7 +25833,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 čtvrtfinále</t>
+          <t>Jihočeský, 4. úroveň, čtvrtfinále</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -25893,7 +25893,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 semifinále</t>
+          <t>Jihočeský, 4. úroveň, semifinále</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -25953,7 +25953,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 finále</t>
+          <t>Jihočeský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -26008,7 +26008,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 Krajská Soutěž</t>
+          <t>Jihočeský, 4. úroveň Krajská Soutěž</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -26055,7 +26055,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>30_Západočeský L40</t>
+          <t>Západočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -26102,7 +26102,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>30_Západočeský L50</t>
+          <t>Západočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -26149,7 +26149,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 skupina A</t>
+          <t>Západočeský, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -26191,7 +26191,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 skupina B</t>
+          <t>Západočeský, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -26233,7 +26233,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 skupina C</t>
+          <t>Západočeský, 4. úroveň, skupina C</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -26275,7 +26275,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>30_Severočeský L40</t>
+          <t>Severočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -26322,7 +26322,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>30_Severočeský L50</t>
+          <t>Severočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -26369,7 +26369,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>30_Severočeský L40 základní část</t>
+          <t>Severočeský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -26429,7 +26429,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>30_Severočeský L40 čtvrtfinále</t>
+          <t>Severočeský, 4. úroveň, čtvrtfinále</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -26484,7 +26484,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>30_Severočeský L40 O 3.místo</t>
+          <t>Severočeský, 4. úroveň O 3.místo</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -26539,7 +26539,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>30_Severočeský L40 finále</t>
+          <t>Severočeský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -26594,7 +26594,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>30_Východočeský L40</t>
+          <t>Východočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -26641,7 +26641,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>30_Východočeský L50</t>
+          <t>Východočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -26688,7 +26688,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>30_Východočeský L50 základní část-sever</t>
+          <t>Východočeský, 5. úroveň, základní část-sever</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -26743,7 +26743,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>30_Východočeský L50 základní část-jih</t>
+          <t>Východočeský, 5. úroveň, základní část-jih</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -26798,7 +26798,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>30_Východočeský L50 finálová skupina</t>
+          <t>Východočeský, 5. úroveň finálová skupina</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -26840,7 +26840,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>30_Východočeský L50 o udržení</t>
+          <t>Východočeský, 5. úroveň o udržení</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -26890,7 +26890,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40</t>
+          <t>Jihomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -26937,7 +26937,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L50</t>
+          <t>Jihomoravský, 5. úroveň</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -26984,7 +26984,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 základní část</t>
+          <t>Jihomoravský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -27049,7 +27049,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 semifinále</t>
+          <t>Jihomoravský, 4. úroveň, semifinále</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 finále</t>
+          <t>Jihomoravský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -27159,7 +27159,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 Krajská soutěž</t>
+          <t>Jihomoravský, 4. úroveň Krajská soutěž</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -27201,7 +27201,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 skupina A</t>
+          <t>Jihomoravský, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -27248,7 +27248,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 finále</t>
+          <t>Jihomoravský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -27298,7 +27298,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 o udržení</t>
+          <t>Jihomoravský, 4. úroveň o udržení</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 skupina B</t>
+          <t>Jihomoravský, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -27390,7 +27390,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 finále</t>
+          <t>Jihomoravský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -27440,7 +27440,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 o udržení</t>
+          <t>Jihomoravský, 4. úroveň o udržení</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -27490,7 +27490,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 finále</t>
+          <t>Jihomoravský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -27540,7 +27540,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40</t>
+          <t>Severomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -27587,7 +27587,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>30_Severomoravský L50</t>
+          <t>Severomoravský, 5. úroveň</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -27626,6 +27626,8 @@
         </is>
       </c>
     </row>
+    <row r="88"/>
+    <row r="89"/>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
@@ -27658,7 +27660,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
+          <t>I.ČNHL (12 CZ) + SNHL (12 Slovensko)</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -27755,6 +27757,7 @@
         </is>
       </c>
     </row>
+    <row r="97"/>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>

--- a/data/S2000_01_FINAL.xlsx
+++ b/data/S2000_01_FINAL.xlsx
@@ -4876,7 +4876,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -27626,8 +27626,6 @@
         </is>
       </c>
     </row>
-    <row r="88"/>
-    <row r="89"/>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
@@ -27757,7 +27755,6 @@
         </is>
       </c>
     </row>
-    <row r="97"/>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
@@ -55729,7 +55726,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -55807,7 +55804,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -55885,7 +55882,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -55963,7 +55960,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -56041,7 +56038,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -56119,7 +56116,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -56197,7 +56194,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -56275,7 +56272,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -56353,7 +56350,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -56431,7 +56428,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -56509,7 +56506,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -56592,7 +56589,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -56675,7 +56672,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -56753,7 +56750,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -57203,7 +57200,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -57281,7 +57278,7 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -57437,7 +57434,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -57515,7 +57512,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -57593,7 +57590,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
